--- a/testdata/lead/bulk_upload/uday_contact.xlsx
+++ b/testdata/lead/bulk_upload/uday_contact.xlsx
@@ -412,57 +412,57 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Aayushman Adiga</v>
+        <v>Anwesha Ganaka</v>
       </c>
       <c r="B2" t="str">
-        <v>aayushman.adiga656@gmail.com</v>
+        <v>anwesha.ganaka423@gmail.com</v>
       </c>
       <c r="C2">
-        <v>8733199544</v>
+        <v>7039375250</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Daevi Butt</v>
+        <v>Mangalya Iyer</v>
       </c>
       <c r="B3" t="str">
-        <v>daevi.butt779@gmail.com</v>
+        <v>mangalya.iyer419@gmail.com</v>
       </c>
       <c r="C3">
-        <v>7932255845</v>
+        <v>9873332318</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Malati Patel</v>
+        <v>Kumari Johar</v>
       </c>
       <c r="B4" t="str">
-        <v>malati.patel956@gmail.com</v>
+        <v>kumari.johar653@gmail.com</v>
       </c>
       <c r="C4">
-        <v>8799417269</v>
+        <v>9774597753</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Triloki Nath Sharma</v>
+        <v>Sarada Bhadresha</v>
       </c>
       <c r="B5" t="str">
-        <v>trilokinath.sharma209@gmail.com</v>
+        <v>sarada.bhadresha623@gmail.com</v>
       </c>
       <c r="C5">
-        <v>7010663210</v>
+        <v>6356972699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Upendra Ganaka</v>
+        <v>Sarala Sharma</v>
       </c>
       <c r="B6" t="str">
-        <v>upendra.ganaka808@gmail.com</v>
+        <v>sarala.sharma953@gmail.com</v>
       </c>
       <c r="C6">
-        <v>8723828968</v>
+        <v>8736671179</v>
       </c>
     </row>
   </sheetData>
